--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quarterly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quarterly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS28"/>
+  <dimension ref="A1:AS53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,7 +650,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPSACBW027SBOG</t>
+          <t>DPSDCBW027SBOG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -674,104 +674,104 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17834.2</v>
+        <v>16494.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="H2" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>17957.9</v>
+        <v>16583.05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="N2" t="n">
         <v>13</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>18133.69</v>
+        <v>16749.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="R2" t="n">
-        <v>3.97</v>
+        <v>4.07</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>18326.22</v>
+        <v>16925.77</v>
       </c>
       <c r="V2" t="n">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="W2" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>18520.56</v>
+        <v>17127.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.31</v>
+        <v>4.86</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>18794.85</v>
+        <v>17382.65</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.66</v>
+        <v>4.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.06</v>
+        <v>6.09</v>
       </c>
       <c r="AH2" t="n">
         <v>12</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>19215.18</v>
+        <v>17739.74</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="AL2" t="n">
-        <v>9.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AM2" t="n">
         <v>13</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>19522.97</v>
+        <v>17938.57</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.53</v>
+        <v>5.98</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.56</v>
+        <v>4.56</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
@@ -781,7 +781,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LTDACBW027SBOG</t>
+          <t>LTDDCBW027SBOG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -805,104 +805,104 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2368.01</v>
+        <v>1568.42</v>
       </c>
       <c r="G3" t="n">
-        <v>6.82</v>
+        <v>11.27</v>
       </c>
       <c r="H3" t="n">
-        <v>5.29</v>
+        <v>7.93</v>
       </c>
       <c r="I3" t="n">
         <v>13</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>2350.11</v>
+        <v>1529.37</v>
       </c>
       <c r="L3" t="n">
-        <v>2.41</v>
+        <v>2.91</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.99</v>
+        <v>-9.59</v>
       </c>
       <c r="N3" t="n">
         <v>13</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>2362.7</v>
+        <v>1528.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>0.93</v>
       </c>
       <c r="R3" t="n">
-        <v>2.16</v>
+        <v>-0.33</v>
       </c>
       <c r="S3" t="n">
         <v>13</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>2399.68</v>
+        <v>1541.11</v>
       </c>
       <c r="V3" t="n">
-        <v>2.65</v>
+        <v>0.15</v>
       </c>
       <c r="W3" t="n">
-        <v>6.41</v>
+        <v>3.45</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>2423.11</v>
+        <v>1571.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.33</v>
+        <v>0.21</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.96</v>
+        <v>8.19</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>2457.45</v>
+        <v>1600.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>4.57</v>
+        <v>4.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.79</v>
+        <v>7.43</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>2511.99</v>
+        <v>1636.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.32</v>
+        <v>7.07</v>
       </c>
       <c r="AL3" t="n">
-        <v>9.18</v>
+        <v>9.31</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>2552.27</v>
+        <v>1632.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.36</v>
+        <v>5.96</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.57</v>
+        <v>-0.8</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
@@ -912,7 +912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ODSACBW027SBOG</t>
+          <t>ODSDCBW027SBOG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -936,104 +936,104 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15466.19</v>
+        <v>14925.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>4.24</v>
+        <v>3.68</v>
       </c>
       <c r="I4" t="n">
         <v>13</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>15607.79</v>
+        <v>15053.68</v>
       </c>
       <c r="L4" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.71</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
         <v>13</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>15770.99</v>
+        <v>15221.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>4.25</v>
+        <v>4.53</v>
       </c>
       <c r="S4" t="n">
         <v>13</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>15926.54</v>
+        <v>15384.66</v>
       </c>
       <c r="V4" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>16097.45</v>
+        <v>15555.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.36</v>
+        <v>4.53</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>16337.4</v>
+        <v>15782.51</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.67</v>
+        <v>4.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="AH4" t="n">
         <v>12</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>16703.19</v>
+        <v>16103.58</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.91</v>
+        <v>5.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>9.26</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AM4" t="n">
         <v>13</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>16970.7</v>
+        <v>16305.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.56</v>
+        <v>5.99</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.56</v>
+        <v>5.12</v>
       </c>
       <c r="AR4" t="n">
         <v>14</v>
@@ -1043,7 +1043,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOTLL</t>
+          <t>LLBDCBW027SBOG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1067,104 +1067,104 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12559.59</v>
+        <v>11423.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>3.12</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>12667.89</v>
+        <v>11514.77</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="M5" t="n">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
         <v>13</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>12838.32</v>
+        <v>11654.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>5.49</v>
+        <v>4.94</v>
       </c>
       <c r="S5" t="n">
         <v>13</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>13028.5</v>
+        <v>11806.81</v>
       </c>
       <c r="V5" t="n">
-        <v>4.53</v>
+        <v>3.99</v>
       </c>
       <c r="W5" t="n">
-        <v>6.06</v>
+        <v>5.34</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>13236.55</v>
+        <v>11981.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.39</v>
+        <v>4.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.54</v>
+        <v>6.06</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>13511.99</v>
+        <v>12205.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>6.66</v>
+        <v>6</v>
       </c>
       <c r="AG5" t="n">
-        <v>8.59</v>
+        <v>7.68</v>
       </c>
       <c r="AH5" t="n">
         <v>12</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>13786.97</v>
+        <v>12420.85</v>
       </c>
       <c r="AK5" t="n">
-        <v>7.39</v>
+        <v>6.58</v>
       </c>
       <c r="AL5" t="n">
-        <v>8.390000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="AM5" t="n">
         <v>13</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>13996.66</v>
+        <v>12592.32</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.43</v>
+        <v>6.65</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.22</v>
+        <v>5.64</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
@@ -1174,7 +1174,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOTCI</t>
+          <t>CILDCBW027SBOG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1198,104 +1198,104 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2791.61</v>
+        <v>2278.69</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H6" t="n">
-        <v>3.99</v>
+        <v>3.29</v>
       </c>
       <c r="I6" t="n">
         <v>13</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>2671.02</v>
+        <v>2166.38</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.22</v>
+        <v>-3.7</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.19</v>
+        <v>-18.3</v>
       </c>
       <c r="N6" t="n">
         <v>13</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>2668.09</v>
+        <v>2154.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.02</v>
+        <v>-3.91</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.44</v>
+        <v>-2.22</v>
       </c>
       <c r="S6" t="n">
         <v>13</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>2676.34</v>
+        <v>2144.79</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.19</v>
+        <v>-5.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>-1.74</v>
       </c>
       <c r="X6" t="n">
         <v>13</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>2700.38</v>
+        <v>2155.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.27</v>
+        <v>-5.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.64</v>
+        <v>1.99</v>
       </c>
       <c r="AC6" t="n">
         <v>14</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>2774.99</v>
+        <v>2199.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.89</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.52</v>
+        <v>8.52</v>
       </c>
       <c r="AH6" t="n">
         <v>12</v>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>2877.02</v>
+        <v>2266.51</v>
       </c>
       <c r="AK6" t="n">
-        <v>7.83</v>
+        <v>5.21</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.54</v>
+        <v>12.68</v>
       </c>
       <c r="AM6" t="n">
         <v>13</v>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>2924.08</v>
+        <v>2307.44</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.26</v>
+        <v>7.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.71</v>
+        <v>7.42</v>
       </c>
       <c r="AR6" t="n">
         <v>14</v>
@@ -1305,7 +1305,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CREACBW027SBOG</t>
+          <t>CREDCBW027SBOG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1329,104 +1329,104 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3004.66</v>
+        <v>2889.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="I7" t="n">
         <v>13</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>3006.15</v>
+        <v>2892.14</v>
       </c>
       <c r="L7" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="N7" t="n">
         <v>13</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>3010.36</v>
+        <v>2896.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="S7" t="n">
         <v>13</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>3023.8</v>
+        <v>2907.99</v>
       </c>
       <c r="V7" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
         <v>13</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>3048.27</v>
+        <v>2932.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>3073.04</v>
+        <v>2954.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="AH7" t="n">
         <v>12</v>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
-        <v>3097.21</v>
+        <v>2977.78</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AM7" t="n">
         <v>13</v>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>3124.94</v>
+        <v>3004.61</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
@@ -1436,7 +1436,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RREACBW027SBOG</t>
+          <t>RREDCBW027SBOG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1460,104 +1460,104 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2611.78</v>
+        <v>2611.31</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
         <v>13</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>2626.51</v>
+        <v>2625.83</v>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="N8" t="n">
         <v>13</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>2646.71</v>
+        <v>2645.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="S8" t="n">
         <v>13</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>2653.97</v>
+        <v>2653.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>2667.84</v>
+        <v>2666.96</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>2683.73</v>
+        <v>2682.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH8" t="n">
         <v>12</v>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
-        <v>2688.32</v>
+        <v>2687.25</v>
       </c>
       <c r="AK8" t="n">
         <v>1.57</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>2697.56</v>
+        <v>2696.11</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
@@ -1567,7 +1567,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLSACBW027SBOG</t>
+          <t>CLSDCBW027SBOG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1698,7 +1698,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CCLACBW027SBOG</t>
+          <t>CCLDCBW027SBOG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1829,17 +1829,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Securities in bank credit</t>
+          <t xml:space="preserve">  Other loans &amp; leases</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBCACBW027SBOG</t>
+          <t>AOLDCBW027SBOG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1853,104 +1853,104 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5383.11</v>
+        <v>1719.54</v>
       </c>
       <c r="G11" t="n">
-        <v>6.93</v>
+        <v>5.53</v>
       </c>
       <c r="H11" t="n">
-        <v>6.08</v>
+        <v>9.19</v>
       </c>
       <c r="I11" t="n">
         <v>13</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>5390.18</v>
+        <v>2010.86</v>
       </c>
       <c r="L11" t="n">
-        <v>4.57</v>
+        <v>23.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0.53</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>13</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>5524.33</v>
+        <v>2133.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.34</v>
+        <v>29.51</v>
       </c>
       <c r="R11" t="n">
-        <v>10.33</v>
+        <v>26.65</v>
       </c>
       <c r="S11" t="n">
         <v>13</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>5613.89</v>
+        <v>2274.39</v>
       </c>
       <c r="V11" t="n">
-        <v>5.84</v>
+        <v>35.21</v>
       </c>
       <c r="W11" t="n">
-        <v>6.64</v>
+        <v>29.22</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>5651.27</v>
+        <v>2377.26</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.98</v>
+        <v>38.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.69</v>
+        <v>19.36</v>
       </c>
       <c r="AC11" t="n">
         <v>14</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>5714.52</v>
+        <v>2497.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.02</v>
+        <v>24.18</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.55</v>
+        <v>21.74</v>
       </c>
       <c r="AH11" t="n">
         <v>12</v>
       </c>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="n">
-        <v>5756.12</v>
+        <v>2595.47</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.2</v>
+        <v>21.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.94</v>
+        <v>16.71</v>
       </c>
       <c r="AM11" t="n">
         <v>13</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>5808.81</v>
+        <v>2664.76</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.47</v>
+        <v>17.16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.71</v>
+        <v>11.11</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
@@ -1960,17 +1960,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Treasury &amp; agency securities</t>
+          <t>Securities in bank credit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TASACBW027SBOG</t>
+          <t>SBCDCBW027SBOG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1984,104 +1984,104 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4401.54</v>
+        <v>5136.79</v>
       </c>
       <c r="G12" t="n">
-        <v>9.220000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="H12" t="n">
-        <v>8.23</v>
+        <v>5.77</v>
       </c>
       <c r="I12" t="n">
         <v>13</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>4415.88</v>
+        <v>5140.32</v>
       </c>
       <c r="L12" t="n">
-        <v>6.88</v>
+        <v>4.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="N12" t="n">
         <v>13</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>4548.21</v>
+        <v>5265.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.24</v>
+        <v>6.08</v>
       </c>
       <c r="R12" t="n">
-        <v>12.54</v>
+        <v>10.13</v>
       </c>
       <c r="S12" t="n">
         <v>13</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>4629.46</v>
+        <v>5344.82</v>
       </c>
       <c r="V12" t="n">
-        <v>7.28</v>
+        <v>5.52</v>
       </c>
       <c r="W12" t="n">
-        <v>7.34</v>
+        <v>6.13</v>
       </c>
       <c r="X12" t="n">
         <v>13</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>4671.85</v>
+        <v>5371.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.71</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>4717.61</v>
+        <v>5419.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.83</v>
+        <v>5.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="AH12" t="n">
         <v>12</v>
       </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="n">
-        <v>4749.54</v>
+        <v>5454.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.43</v>
+        <v>3.58</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AM12" t="n">
         <v>13</v>
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>4802.88</v>
+        <v>5505.62</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.75</v>
+        <v>3.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.57</v>
+        <v>3.82</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2091,17 +2091,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cash assets</t>
+          <t xml:space="preserve">  Treasury &amp; agency securities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CASACBW027SBOG</t>
+          <t>TASDCBW027SBOG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2115,104 +2115,104 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3270.84</v>
+        <v>4237.18</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.86</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.46</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
         <v>13</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>3302.93</v>
+        <v>4249.53</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.13</v>
+        <v>6.57</v>
       </c>
       <c r="M13" t="n">
-        <v>3.98</v>
+        <v>1.17</v>
       </c>
       <c r="N13" t="n">
         <v>13</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>3286.09</v>
+        <v>4373.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.61</v>
+        <v>7.97</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.02</v>
+        <v>12.24</v>
       </c>
       <c r="S13" t="n">
         <v>13</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>3262.95</v>
+        <v>4445.88</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.89</v>
+        <v>6.91</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.79</v>
+        <v>6.74</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>2996.88</v>
+        <v>4480.32</v>
       </c>
       <c r="AA13" t="n">
-        <v>-8.380000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>-28.84</v>
+        <v>3.13</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>3004.84</v>
+        <v>4513.46</v>
       </c>
       <c r="AF13" t="n">
-        <v>-9.029999999999999</v>
+        <v>6.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>2.99</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
       </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="n">
-        <v>3057.99</v>
+        <v>4538.61</v>
       </c>
       <c r="AK13" t="n">
-        <v>-6.94</v>
+        <v>3.76</v>
       </c>
       <c r="AL13" t="n">
-        <v>7.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM13" t="n">
         <v>13</v>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>3071.56</v>
+        <v>4589.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>-5.87</v>
+        <v>3.24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.79</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
@@ -2222,17 +2222,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Cash assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TLAACBW027SBOG</t>
+          <t>CASDCBW027SBOG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2246,104 +2246,104 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>23588.48</v>
+        <v>2013.95</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>-4.97</v>
       </c>
       <c r="H14" t="n">
-        <v>2.87</v>
+        <v>-7.11</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>23798.57</v>
+        <v>1946.46</v>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>3.61</v>
+        <v>-12.75</v>
       </c>
       <c r="N14" t="n">
         <v>13</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>24161.9</v>
+        <v>1884.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.79</v>
+        <v>-10.37</v>
       </c>
       <c r="R14" t="n">
-        <v>6.25</v>
+        <v>-12.23</v>
       </c>
       <c r="S14" t="n">
         <v>13</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>24470.71</v>
+        <v>1915.75</v>
       </c>
       <c r="V14" t="n">
-        <v>4.48</v>
+        <v>-6.61</v>
       </c>
       <c r="W14" t="n">
-        <v>5.21</v>
+        <v>6.91</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>24534.88</v>
+        <v>1843.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.01</v>
+        <v>-8.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>-14.31</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>24917.14</v>
+        <v>1889.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>4.7</v>
+        <v>-2.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.38</v>
+        <v>10.34</v>
       </c>
       <c r="AH14" t="n">
         <v>12</v>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="n">
-        <v>25402.34</v>
+        <v>1900.79</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.13</v>
+        <v>0.89</v>
       </c>
       <c r="AL14" t="n">
-        <v>8.02</v>
+        <v>2.51</v>
       </c>
       <c r="AM14" t="n">
         <v>13</v>
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>25727.47</v>
+        <v>1841.3</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.14</v>
+        <v>-3.89</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.22</v>
+        <v>-11.94</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -2353,22 +2353,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H.8 · All commercial banks (weekly, SA unless noted)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Borrowings</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>H8_BORROW</t>
+          <t>TLADCBW027SBOG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2377,104 +2377,104 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2225.63</v>
+        <v>20438.77</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.27</v>
+        <v>2.49</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.17</v>
+        <v>3.06</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>2171.48</v>
+        <v>20516.77</v>
       </c>
       <c r="L15" t="n">
-        <v>-10.05</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.380000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="N15" t="n">
         <v>13</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>2221.91</v>
+        <v>20747.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.29</v>
+        <v>3.04</v>
       </c>
       <c r="R15" t="n">
-        <v>9.619999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="S15" t="n">
         <v>13</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>2288.83</v>
+        <v>21057.73</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.01</v>
+        <v>3.81</v>
       </c>
       <c r="W15" t="n">
-        <v>12.6</v>
+        <v>6.12</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>2167.01</v>
+        <v>21231.13</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.63</v>
+        <v>3.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>-19.65</v>
+        <v>3.33</v>
       </c>
       <c r="AC15" t="n">
         <v>14</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>2229.88</v>
+        <v>21576.41</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.69</v>
+        <v>5.16</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.12</v>
+        <v>6.67</v>
       </c>
       <c r="AH15" t="n">
         <v>12</v>
       </c>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="n">
-        <v>2277.47</v>
+        <v>21962.95</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>5.86</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.81</v>
+        <v>7.36</v>
       </c>
       <c r="AM15" t="n">
         <v>13</v>
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>2294.66</v>
+        <v>22148.39</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.25</v>
+        <v>5.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -2484,22 +2484,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H.8 · Large domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Domestically chartered banks, total (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DPSLCBW027SBOG</t>
+          <t>BOR_D</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2508,104 +2508,104 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11226.37</v>
+        <v>1324.49</v>
       </c>
       <c r="G16" t="n">
-        <v>1.78</v>
+        <v>-2.12</v>
       </c>
       <c r="H16" t="n">
-        <v>2.92</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>13</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>11276.03</v>
+        <v>1283.33</v>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>-7.39</v>
       </c>
       <c r="M16" t="n">
-        <v>1.78</v>
+        <v>-11.86</v>
       </c>
       <c r="N16" t="n">
         <v>13</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>11379.4</v>
+        <v>1320.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>-5.16</v>
       </c>
       <c r="R16" t="n">
-        <v>3.72</v>
+        <v>12.16</v>
       </c>
       <c r="S16" t="n">
         <v>13</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>11509.72</v>
+        <v>1348.52</v>
       </c>
       <c r="V16" t="n">
-        <v>3.26</v>
+        <v>-0.5</v>
       </c>
       <c r="W16" t="n">
-        <v>4.66</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>13</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>11650.74</v>
+        <v>1255.56</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.78</v>
+        <v>-5.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.99</v>
+        <v>-24.85</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>11847.5</v>
+        <v>1329.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>5.07</v>
+        <v>3.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.93</v>
+        <v>25.69</v>
       </c>
       <c r="AH16" t="n">
         <v>12</v>
       </c>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
-        <v>12123.44</v>
+        <v>1369.59</v>
       </c>
       <c r="AK16" t="n">
-        <v>6.54</v>
+        <v>3.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>9.65</v>
+        <v>12.64</v>
       </c>
       <c r="AM16" t="n">
         <v>13</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>12274.79</v>
+        <v>1352.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.65</v>
+        <v>0.31</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.09</v>
+        <v>-4.86</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -2615,17 +2615,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H.8 · Large domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Large time deposits</t>
+          <t>Total deposits</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LTDLCBW027SBOG</t>
+          <t>DPSLCBW027SBOG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2639,104 +2639,104 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>833.1900000000001</v>
+        <v>11226.37</v>
       </c>
       <c r="G17" t="n">
-        <v>6.13</v>
+        <v>1.78</v>
       </c>
       <c r="H17" t="n">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>805.65</v>
+        <v>11276.03</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.68</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>-12.58</v>
+        <v>1.78</v>
       </c>
       <c r="N17" t="n">
         <v>13</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>797.36</v>
+        <v>11379.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.79</v>
+        <v>2.65</v>
       </c>
       <c r="R17" t="n">
-        <v>-4.06</v>
+        <v>3.72</v>
       </c>
       <c r="S17" t="n">
         <v>13</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>806.62</v>
+        <v>11509.72</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.73</v>
+        <v>3.26</v>
       </c>
       <c r="W17" t="n">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>826.23</v>
+        <v>11650.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.84</v>
+        <v>3.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.08</v>
+        <v>4.99</v>
       </c>
       <c r="AC17" t="n">
         <v>14</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>860.47</v>
+        <v>11847.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>6.8</v>
+        <v>5.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>17.64</v>
+        <v>6.93</v>
       </c>
       <c r="AH17" t="n">
         <v>12</v>
       </c>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
-        <v>900.25</v>
+        <v>12123.44</v>
       </c>
       <c r="AK17" t="n">
-        <v>12.9</v>
+        <v>6.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>19.82</v>
+        <v>9.65</v>
       </c>
       <c r="AM17" t="n">
         <v>13</v>
       </c>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="n">
-        <v>897.17</v>
+        <v>12274.79</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.23</v>
+        <v>6.65</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-1.36</v>
+        <v>5.09</v>
       </c>
       <c r="AR17" t="n">
         <v>14</v>
@@ -2746,17 +2746,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H.8 · Large domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loans &amp; leases</t>
+          <t xml:space="preserve">  Large time deposits</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LLBLCBW027SBOG</t>
+          <t>LTDLCBW027SBOG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2770,104 +2770,104 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7071.26</v>
+        <v>833.1900000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.14</v>
+        <v>6.13</v>
       </c>
       <c r="H18" t="n">
-        <v>2.77</v>
+        <v>1.93</v>
       </c>
       <c r="I18" t="n">
         <v>13</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>7127.05</v>
+        <v>805.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>-2.68</v>
       </c>
       <c r="M18" t="n">
-        <v>3.19</v>
+        <v>-12.58</v>
       </c>
       <c r="N18" t="n">
         <v>13</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>7221.46</v>
+        <v>797.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.39</v>
+        <v>-3.79</v>
       </c>
       <c r="R18" t="n">
-        <v>5.41</v>
+        <v>-4.06</v>
       </c>
       <c r="S18" t="n">
         <v>13</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>7325.51</v>
+        <v>806.62</v>
       </c>
       <c r="V18" t="n">
-        <v>4.31</v>
+        <v>-2.73</v>
       </c>
       <c r="W18" t="n">
-        <v>5.89</v>
+        <v>4.73</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>7443.47</v>
+        <v>826.23</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.26</v>
+        <v>-0.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.6</v>
+        <v>10.08</v>
       </c>
       <c r="AC18" t="n">
         <v>14</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>7598.29</v>
+        <v>860.47</v>
       </c>
       <c r="AF18" t="n">
-        <v>6.61</v>
+        <v>6.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>8.58</v>
+        <v>17.64</v>
       </c>
       <c r="AH18" t="n">
         <v>12</v>
       </c>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
-        <v>7763.27</v>
+        <v>900.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>7.5</v>
+        <v>12.9</v>
       </c>
       <c r="AL18" t="n">
-        <v>8.970000000000001</v>
+        <v>19.82</v>
       </c>
       <c r="AM18" t="n">
         <v>13</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>7871.74</v>
+        <v>897.17</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.46</v>
+        <v>11.23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.71</v>
+        <v>-1.36</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -2877,17 +2877,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H.8 · Small domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t xml:space="preserve">  Other deposits (ex large time)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DPSSCBW027SBOG</t>
+          <t>ODSLCBW027SBOG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2901,104 +2901,104 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5268.03</v>
+        <v>10393.18</v>
       </c>
       <c r="G19" t="n">
-        <v>4.35</v>
+        <v>1.45</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>13</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>5307.02</v>
+        <v>10470.38</v>
       </c>
       <c r="L19" t="n">
-        <v>4.31</v>
+        <v>1.99</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>13</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>5369.97</v>
+        <v>10582.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.28</v>
+        <v>3.17</v>
       </c>
       <c r="R19" t="n">
-        <v>4.83</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>13</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>5416.05</v>
+        <v>10703.1</v>
       </c>
       <c r="V19" t="n">
-        <v>4.47</v>
+        <v>3.75</v>
       </c>
       <c r="W19" t="n">
-        <v>3.48</v>
+        <v>4.66</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>5476.93</v>
+        <v>10824.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.97</v>
+        <v>4.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="AC19" t="n">
         <v>14</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>5535.14</v>
+        <v>10987.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.32</v>
+        <v>6.14</v>
       </c>
       <c r="AH19" t="n">
         <v>12</v>
       </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="n">
-        <v>5616.3</v>
+        <v>11223.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>4.59</v>
+        <v>6.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>6</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AM19" t="n">
         <v>13</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
-        <v>5663.78</v>
+        <v>11377.62</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.57</v>
+        <v>6.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.42</v>
+        <v>5.62</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3008,17 +3008,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H.8 · Small domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Large time deposits</t>
+          <t>Loans &amp; leases</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LTDSCBW027SBOG</t>
+          <t>LLBLCBW027SBOG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3032,104 +3032,104 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>735.23</v>
+        <v>7071.26</v>
       </c>
       <c r="G20" t="n">
-        <v>17.73</v>
+        <v>1.14</v>
       </c>
       <c r="H20" t="n">
-        <v>15.27</v>
+        <v>2.77</v>
       </c>
       <c r="I20" t="n">
         <v>13</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>723.72</v>
+        <v>7127.05</v>
       </c>
       <c r="L20" t="n">
-        <v>9.93</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.12</v>
+        <v>3.19</v>
       </c>
       <c r="N20" t="n">
         <v>13</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>730.73</v>
+        <v>7221.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.64</v>
+        <v>3.39</v>
       </c>
       <c r="R20" t="n">
-        <v>3.94</v>
+        <v>5.41</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>734.49</v>
+        <v>7325.51</v>
       </c>
       <c r="V20" t="n">
-        <v>3.51</v>
+        <v>4.31</v>
       </c>
       <c r="W20" t="n">
-        <v>2.07</v>
+        <v>5.89</v>
       </c>
       <c r="X20" t="n">
         <v>13</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>745.5</v>
+        <v>7443.47</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>5.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.13</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
         <v>14</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>739.67</v>
+        <v>7598.29</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.21</v>
+        <v>6.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.09</v>
+        <v>8.58</v>
       </c>
       <c r="AH20" t="n">
         <v>12</v>
       </c>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="n">
-        <v>735.91</v>
+        <v>7763.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.71</v>
+        <v>7.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>-2.02</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AM20" t="n">
         <v>13</v>
       </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>735.73</v>
+        <v>7871.74</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.17</v>
+        <v>7.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.1</v>
+        <v>5.71</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -3139,17 +3139,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H.8 · Small domestically chartered banks (weekly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Loans &amp; leases</t>
+          <t xml:space="preserve">  C&amp;I loans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LLBSCBW027SBOG</t>
+          <t>CIL_LARGE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3163,104 +3163,104 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4351.75</v>
+        <v>1580.15</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>0.21</v>
       </c>
       <c r="H21" t="n">
-        <v>1.97</v>
+        <v>4.17</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>4387.72</v>
+        <v>1474.47</v>
       </c>
       <c r="L21" t="n">
-        <v>2.91</v>
+        <v>-5.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>-24.19</v>
       </c>
       <c r="N21" t="n">
         <v>13</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>4432.88</v>
+        <v>1462.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.18</v>
+        <v>-5.81</v>
       </c>
       <c r="R21" t="n">
-        <v>4.18</v>
+        <v>-3.09</v>
       </c>
       <c r="S21" t="n">
         <v>13</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>4481.3</v>
+        <v>1446.73</v>
       </c>
       <c r="V21" t="n">
-        <v>3.48</v>
+        <v>-7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>4.44</v>
+        <v>-4.36</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>4538.42</v>
+        <v>1453.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.29</v>
+        <v>-8</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>14</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>4607.23</v>
+        <v>1492.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>6.2</v>
+        <v>11.24</v>
       </c>
       <c r="AH21" t="n">
         <v>12</v>
       </c>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="n">
-        <v>4657.59</v>
+        <v>1547.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>5.07</v>
+        <v>5.76</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.44</v>
+        <v>15.37</v>
       </c>
       <c r="AM21" t="n">
         <v>13</v>
       </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
-        <v>4720.58</v>
+        <v>1573.93</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.34</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.52</v>
+        <v>7.09</v>
       </c>
       <c r="AR21" t="n">
         <v>14</v>
@@ -3270,17 +3270,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deposits: demand + other liquid + small time</t>
+          <t xml:space="preserve">  CRE loans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>H6_TOTAL</t>
+          <t>CRELCBW027SBOG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3290,132 +3290,128 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17640.27</v>
+        <v>900.61</v>
       </c>
       <c r="G22" t="n">
-        <v>1.83</v>
+        <v>-2.69</v>
       </c>
       <c r="H22" t="n">
-        <v>3.93</v>
+        <v>-3.44</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>17784.17</v>
+        <v>891.04</v>
       </c>
       <c r="L22" t="n">
-        <v>2.24</v>
+        <v>-3.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>-4.19</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>17913.07</v>
+        <v>882.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.03</v>
+        <v>-3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>2.93</v>
+        <v>-3.95</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>18058.3</v>
+        <v>880.53</v>
       </c>
       <c r="V22" t="n">
-        <v>3.36</v>
+        <v>-3.08</v>
       </c>
       <c r="W22" t="n">
-        <v>3.28</v>
+        <v>-0.71</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>18207.57</v>
+        <v>887.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>-1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>18461.47</v>
+        <v>890.98</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.81</v>
+        <v>-0.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.7</v>
+        <v>1.45</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
-        <v>18797.33</v>
+        <v>897.4400000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.94</v>
+        <v>1.74</v>
       </c>
       <c r="AL22" t="n">
-        <v>7.48</v>
+        <v>2.93</v>
       </c>
       <c r="AM22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="n">
-        <v>19058.4</v>
+        <v>905.7</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.54</v>
+        <v>2.86</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.67</v>
+        <v>3.73</v>
       </c>
       <c r="AR22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AS22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Demand deposits</t>
+          <t xml:space="preserve">  Residential real estate loans</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEMDEPSL</t>
+          <t>RRELCBW027SBOG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3425,132 +3421,128 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5404.43</v>
+        <v>1643.73</v>
       </c>
       <c r="G23" t="n">
-        <v>8.33</v>
+        <v>0.61</v>
       </c>
       <c r="H23" t="n">
-        <v>9.800000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>5525.73</v>
+        <v>1648.23</v>
       </c>
       <c r="L23" t="n">
-        <v>9.35</v>
+        <v>0.42</v>
       </c>
       <c r="M23" t="n">
-        <v>9.279999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>5574.7</v>
+        <v>1656.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.31</v>
+        <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>3.59</v>
+        <v>1.96</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>5653.3</v>
+        <v>1653.41</v>
       </c>
       <c r="V23" t="n">
-        <v>7.08</v>
+        <v>0.47</v>
       </c>
       <c r="W23" t="n">
-        <v>5.76</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>6191.63</v>
+        <v>1657.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.57</v>
+        <v>0.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>43.88</v>
+        <v>0.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>6751.43</v>
+        <v>1660.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>22.18</v>
+        <v>0.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>41.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="n">
-        <v>6935.87</v>
+        <v>1659.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>24.42</v>
+        <v>0.17</v>
       </c>
       <c r="AL23" t="n">
-        <v>11.38</v>
+        <v>-0.35</v>
       </c>
       <c r="AM23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="n">
-        <v>7107.9</v>
+        <v>1659.76</v>
       </c>
       <c r="AP23" t="n">
-        <v>25.73</v>
+        <v>0.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.3</v>
+        <v>0.17</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AS23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other liquid deposits (savings incl. MMDA + OCDs)</t>
+          <t xml:space="preserve">  Consumer loans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OLD_SPLICED</t>
+          <t>CLSLCBW027SBOG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3560,132 +3552,128 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10647.63</v>
+        <v>1580.03</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.28</v>
+        <v>1.61</v>
       </c>
       <c r="H24" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>10705.2</v>
+        <v>1518.06</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.14</v>
+        <v>-2.68</v>
       </c>
       <c r="M24" t="n">
-        <v>2.18</v>
+        <v>-14.79</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>10807.7</v>
+        <v>1518.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>-2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>3.89</v>
+        <v>0.01</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>10878.73</v>
+        <v>1515.71</v>
       </c>
       <c r="V24" t="n">
-        <v>3.02</v>
+        <v>-3.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.66</v>
+        <v>-0.63</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>10503.43</v>
+        <v>1532.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>-1.35</v>
+        <v>-2.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>-13.1</v>
+        <v>4.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>10210.83</v>
+        <v>1547.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>-4.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>-10.69</v>
+        <v>3.75</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="n">
-        <v>10359.1</v>
+        <v>1566.9</v>
       </c>
       <c r="AK24" t="n">
-        <v>-4.15</v>
+        <v>3.21</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.94</v>
+        <v>5.22</v>
       </c>
       <c r="AM24" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="n">
-        <v>10444.5</v>
+        <v>1581.16</v>
       </c>
       <c r="AP24" t="n">
-        <v>-3.99</v>
+        <v>4.32</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.34</v>
+        <v>3.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AS24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Small-denomination time deposits</t>
+          <t xml:space="preserve">    Credit card &amp; revolving</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>STDSL</t>
+          <t>CCLLCBW027SBOG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3695,132 +3683,128 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1588.2</v>
+        <v>983.37</v>
       </c>
       <c r="G25" t="n">
-        <v>2.57</v>
+        <v>5.17</v>
       </c>
       <c r="H25" t="n">
-        <v>-10.11</v>
+        <v>3.91</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>1553.23</v>
+        <v>953.26</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.16</v>
+        <v>-0.1</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.52</v>
+        <v>-11.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1530.67</v>
+        <v>947.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.5</v>
+        <v>-1.8</v>
       </c>
       <c r="R25" t="n">
-        <v>-5.69</v>
+        <v>-2.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>1526.27</v>
+        <v>952.0599999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.43</v>
+        <v>-2.25</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.14</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>1512.5</v>
+        <v>961.5700000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>-4.77</v>
+        <v>-2.22</v>
       </c>
       <c r="AB25" t="n">
-        <v>-3.56</v>
+        <v>4.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>1499.2</v>
+        <v>971.66</v>
       </c>
       <c r="AF25" t="n">
-        <v>-3.48</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.47</v>
+        <v>4.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="n">
-        <v>1502.37</v>
+        <v>986.51</v>
       </c>
       <c r="AK25" t="n">
-        <v>-1.85</v>
+        <v>4.07</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.85</v>
+        <v>6.25</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="n">
-        <v>1506</v>
+        <v>994.9</v>
       </c>
       <c r="AP25" t="n">
-        <v>-1.33</v>
+        <v>4.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.97</v>
+        <v>3.44</v>
       </c>
       <c r="AR25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AS25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Retail money market funds (memo)</t>
+          <t xml:space="preserve">  Other loans &amp; leases</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RMFSL</t>
+          <t>AOLLCBW027SBOG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3830,122 +3814,3413 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2601.23</v>
+        <v>1366.74</v>
       </c>
       <c r="G26" t="n">
-        <v>18.64</v>
+        <v>5.09</v>
       </c>
       <c r="H26" t="n">
-        <v>16.24</v>
+        <v>9.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>2679.1</v>
+        <v>1595.24</v>
       </c>
       <c r="L26" t="n">
-        <v>17.65</v>
+        <v>22.98</v>
       </c>
       <c r="M26" t="n">
-        <v>12.52</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>2806.7</v>
+        <v>1702.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>17.06</v>
+        <v>30.17</v>
       </c>
       <c r="R26" t="n">
-        <v>20.46</v>
+        <v>29.59</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>2907.23</v>
+        <v>1829.13</v>
       </c>
       <c r="V26" t="n">
-        <v>16.05</v>
+        <v>36.86</v>
       </c>
       <c r="W26" t="n">
-        <v>15.12</v>
+        <v>33.38</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>2962.07</v>
+        <v>1911.87</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.87</v>
+        <v>39.89</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.76</v>
+        <v>19.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>2962.47</v>
+        <v>2006.79</v>
       </c>
       <c r="AF26" t="n">
-        <v>10.58</v>
+        <v>25.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.05</v>
+        <v>21.39</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="n">
-        <v>3022.67</v>
+        <v>2092.63</v>
       </c>
       <c r="AK26" t="n">
-        <v>7.69</v>
+        <v>22.95</v>
       </c>
       <c r="AL26" t="n">
-        <v>8.380000000000001</v>
+        <v>18.24</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="n">
-        <v>3063.35</v>
+        <v>2151.18</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.37</v>
+        <v>17.61</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.49</v>
+        <v>11.67</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Securities in bank credit</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SBCLCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3917.94</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>3929.28</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>4046.32</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="R27" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>4118.38</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="W27" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>4134.84</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>4176.07</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>4203.74</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>4251.35</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Levels are quarter averages of the weekly (H.8, week-ending Wednesday) or monthly (H.6) data, $bn. YoY = quarter average vs the same quarter a year earlier. LQA = linked-quarter annualized, compounded: ((Q avg / prior-Q avg)^4 − 1). QTD = quarter still in progress (average of the observations so far; hover for count); its YoY/LQA compare that partial average with full prior quarters. Borrowings are NSA, so their LQA includes seasonal swings. H.6 'other liquid deposits' splices savings + OCDs (pre-May 2020) with MDLM. Source: Federal Reserve H.8 and H.6 via FRED.</t>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Treasury &amp; agency securities</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TASLCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3384.39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>13</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>3403.83</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>3518.96</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="R28" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>3581.58</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="W28" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>3602.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>3627.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="n">
+        <v>3646.17</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="n">
+        <v>3684.48</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cash assets</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CASLCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1525.92</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-15.18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>1461.39</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-15.87</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>1395.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-16.14</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>1426.41</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="W29" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>1349.33</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-11.57</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-19.92</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>1387.27</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="n">
+        <v>1400.71</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="n">
+        <v>1349.78</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-13.77</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TLALCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13991.73</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>14040.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>14216.07</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>13</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>14467.84</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="W30" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="X30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>14562.91</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>14816.6</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="n">
+        <v>15141.66</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="n">
+        <v>15255.31</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H.8 · Large domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BOR_L</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1000.4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>13</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>977.0700000000001</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>1011.33</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R31" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="S31" t="n">
+        <v>13</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>1052.66</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="X31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>977.51</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-25.64</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>1044.92</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="n">
+        <v>1071.82</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="n">
+        <v>1060.87</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Total deposits</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DPSSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5268.03</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>5307.02</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>5369.97</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="S32" t="n">
+        <v>13</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>5416.05</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>5476.93</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>5535.14</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="n">
+        <v>5616.3</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="n">
+        <v>5663.78</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Large time deposits</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LTDSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>735.23</v>
+      </c>
+      <c r="G33" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>723.72</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>730.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="S33" t="n">
+        <v>13</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>734.49</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="X33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>745.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>739.67</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="n">
+        <v>735.91</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>735.73</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other deposits (ex large time)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ODSSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4532.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="I34" t="n">
+        <v>13</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>4583.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>4639.24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>4681.56</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X34" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>4731.43</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>4795.47</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
+        <v>4880.39</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="n">
+        <v>4928.05</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Loans &amp; leases</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LLBSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>4351.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I35" t="n">
+        <v>13</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>4387.72</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>4432.88</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>13</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>4481.3</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="X35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>4538.42</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>4607.23</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="n">
+        <v>4657.59</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="n">
+        <v>4720.58</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C&amp;I loans</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CILSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>698.54</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>691.91</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>691.28</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="S36" t="n">
+        <v>13</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>698.0599999999999</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>701.6799999999999</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>706.98</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="n">
+        <v>719.29</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>733.51</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CRE loans</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CRESCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1988.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>2001.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N37" t="n">
+        <v>13</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>2014.45</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>13</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v>2027.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>2044.7</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>2063.86</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>2080.34</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>2098.92</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Residential real estate loans</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RRESCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>967.58</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I38" t="n">
+        <v>13</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>977.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>989.54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="S38" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>999.74</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>1009.76</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>1022.24</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="n">
+        <v>1028.17</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="n">
+        <v>1036.35</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Consumer loans</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLSSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-13.88</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-41.22</v>
+      </c>
+      <c r="N39" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>306.43</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-12.44</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S39" t="n">
+        <v>13</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>310.78</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-11.66</v>
+      </c>
+      <c r="W39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>338.23</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Credit card &amp; revolving</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CCLSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I40" t="n">
+        <v>13</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="S40" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>95.31999999999999</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W40" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="X40" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other loans &amp; leases</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AOLSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>415.62</v>
+      </c>
+      <c r="L41" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M41" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="N41" t="n">
+        <v>13</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>431.18</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="R41" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="S41" t="n">
+        <v>13</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="V41" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="W41" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="X41" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>465.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="n">
+        <v>490.31</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="n">
+        <v>502.84</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="n">
+        <v>513.59</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Securities in bank credit</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SBCSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1218.86</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1211.04</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="N42" t="n">
+        <v>13</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>1219.53</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S42" t="n">
+        <v>13</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>1226.44</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X42" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>1236.99</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>1243.81</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="n">
+        <v>1250.54</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="n">
+        <v>1254.27</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Treasury &amp; agency securities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TASSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>852.78</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="I43" t="n">
+        <v>13</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>845.71</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="N43" t="n">
+        <v>13</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>855.01</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>864.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W43" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>878.01</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>885.63</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="n">
+        <v>892.4299999999999</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="n">
+        <v>905.47</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cash assets</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CASSCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>488.03</v>
+      </c>
+      <c r="G44" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="H44" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>485.07</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>13</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>488.98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>489.35</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="X44" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>493.85</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="n">
+        <v>501.8</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="n">
+        <v>500.09</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="n">
+        <v>491.52</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TLASCBW027SBOG</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>6447.04</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>6476.28</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N45" t="n">
+        <v>13</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>6531.39</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>6589.88</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="X45" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>6668.22</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="n">
+        <v>6759.81</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="n">
+        <v>6821.29</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="n">
+        <v>6893.08</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>H.8 · Small domestically chartered banks (weekly, SA unless noted)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BOR_S</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-19.82</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-42.22</v>
+      </c>
+      <c r="I46" t="n">
+        <v>13</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>306.27</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-24.43</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-20.24</v>
+      </c>
+      <c r="N46" t="n">
+        <v>13</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>309.36</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-20.24</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>13</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>295.86</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-20.41</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="X46" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>278.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-14.21</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="n">
+        <v>297.77</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="n">
+        <v>291.77</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deposits: demand + other liquid + small time</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>H6_TOTAL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>17640.27</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>17784.17</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>17913.07</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>18058.3</v>
+      </c>
+      <c r="V47" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>18207.57</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>18461.47</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
+        <v>18797.33</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="n">
+        <v>19058.4</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Demand deposits</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEMDEPSL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5404.43</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="H48" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>5525.73</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>5574.7</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>5653.3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="W48" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>6191.63</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="n">
+        <v>6751.43</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="n">
+        <v>6935.87</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="n">
+        <v>7107.9</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other liquid deposits (savings incl. MMDA + OCDs)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OLD_SPLICED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>10647.63</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>10705.2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>10807.7</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>10878.73</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>10503.43</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="n">
+        <v>10210.83</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>-10.69</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="n">
+        <v>10359.1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="n">
+        <v>10444.5</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Small-denomination time deposits</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>STDSL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1588.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-10.11</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>1553.23</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>1530.67</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>1526.27</v>
+      </c>
+      <c r="V50" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="n">
+        <v>1512.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="n">
+        <v>1499.2</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="n">
+        <v>1502.37</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="n">
+        <v>1506</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H.6 · Money stock, all depository institutions (monthly, SA)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Retail money market funds (memo)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RMFSL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2601.23</v>
+      </c>
+      <c r="G51" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="H51" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>2679.1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="M51" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>2806.7</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="R51" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>2907.23</v>
+      </c>
+      <c r="V51" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="W51" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>2962.07</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="n">
+        <v>2962.47</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
+        <v>3022.67</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="n">
+        <v>3063.35</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Levels are quarter averages of the weekly (H.8, week-ending Wednesday) or monthly (H.6) data, $bn. YoY = quarter average vs the same quarter a year earlier. LQA = linked-quarter annualized, compounded: ((Q avg / prior-Q avg)^4 − 1). QTD = quarter still in progress (average of the observations so far; hover for count); its YoY/LQA compare that partial average with full prior quarters. Borrowings are NSA, so their LQA includes seasonal swings. H.6 'other liquid deposits' splices savings + OCDs (pre-May 2020) with MDLM. Large-bank C&amp;I = domestic minus small (both Fed H.8). Source: Federal Reserve H.8 and H.6 via FRED.</t>
         </is>
       </c>
     </row>

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS53"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +646,31 @@
           <t>Q3 2026 partial (QTD)</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2026 avg level ($bn)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2026 YoY %</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2026 LQA %</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2026 obs in qtr</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2026 partial (QTD)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -765,18 +790,35 @@
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>17938.57</v>
+        <v>17939.06</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
       </c>
       <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>18129.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -896,18 +938,35 @@
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1632.9</v>
+        <v>1633.07</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.8</v>
+        <v>-0.76</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>1662.12</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1027,7 +1086,7 @@
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>16305.67</v>
+        <v>16306</v>
       </c>
       <c r="AP4" t="n">
         <v>5.99</v>
@@ -1039,6 +1098,23 @@
         <v>14</v>
       </c>
       <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>16467.18</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1158,18 +1234,35 @@
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>12592.32</v>
+        <v>12594.27</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.65</v>
+        <v>6.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
       </c>
       <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>12751.96</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1289,18 +1382,35 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>2307.44</v>
+        <v>2307.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.42</v>
+        <v>7.45</v>
       </c>
       <c r="AR6" t="n">
         <v>14</v>
       </c>
       <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>2359.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1420,18 +1530,35 @@
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>3004.61</v>
+        <v>3005.76</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
       </c>
       <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>3031.84</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1551,18 +1678,35 @@
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>2696.11</v>
+        <v>2696.66</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
       </c>
       <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>2695.85</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1682,10 +1826,10 @@
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>1919.39</v>
+        <v>1919.37</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="AQ9" t="n">
         <v>5.5</v>
@@ -1694,6 +1838,23 @@
         <v>14</v>
       </c>
       <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>1935.67</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1825,6 +1986,23 @@
         <v>14</v>
       </c>
       <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>1104.06</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1944,18 +2122,35 @@
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>2664.76</v>
+        <v>2664.87</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.16</v>
+        <v>17.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.11</v>
+        <v>11.13</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
       </c>
       <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>2729.57</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2075,18 +2270,35 @@
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>5505.62</v>
+        <v>5505.5</v>
       </c>
       <c r="AP12" t="n">
         <v>3.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
       </c>
       <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>5442.53</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2206,18 +2418,35 @@
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>4589.96</v>
+        <v>4590.04</v>
       </c>
       <c r="AP13" t="n">
         <v>3.24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
       </c>
       <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>4526.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2337,18 +2566,35 @@
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>1841.3</v>
+        <v>1840.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>-3.89</v>
+        <v>-3.94</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-11.94</v>
+        <v>-12.14</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
       </c>
       <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>1879.34</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2468,7 +2714,7 @@
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>22148.39</v>
+        <v>22148.59</v>
       </c>
       <c r="AP15" t="n">
         <v>5.18</v>
@@ -2480,6 +2726,23 @@
         <v>14</v>
       </c>
       <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>22336.09</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2599,18 +2862,35 @@
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>1352.64</v>
+        <v>1352.71</v>
       </c>
       <c r="AP16" t="n">
         <v>0.31</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-4.86</v>
+        <v>-4.84</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
       </c>
       <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>1374.82</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2742,6 +3022,23 @@
         <v>14</v>
       </c>
       <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>12441.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2873,6 +3170,23 @@
         <v>14</v>
       </c>
       <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>914.62</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3004,6 +3318,23 @@
         <v>14</v>
       </c>
       <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>11526.39</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3135,6 +3466,23 @@
         <v>14</v>
       </c>
       <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>7983.45</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3266,6 +3614,23 @@
         <v>14</v>
       </c>
       <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>1616.81</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3397,6 +3762,23 @@
         <v>14</v>
       </c>
       <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>915.78</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3528,6 +3910,23 @@
         <v>14</v>
       </c>
       <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>1656.65</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3659,6 +4058,23 @@
         <v>14</v>
       </c>
       <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>1583.32</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3790,6 +4206,23 @@
         <v>14</v>
       </c>
       <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>1000.63</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3921,6 +4354,23 @@
         <v>14</v>
       </c>
       <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>2210.88</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4052,6 +4502,23 @@
         <v>14</v>
       </c>
       <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>4199.79</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4183,6 +4650,23 @@
         <v>14</v>
       </c>
       <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>3623.86</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-6.42</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4314,6 +4798,23 @@
         <v>14</v>
       </c>
       <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>1397.23</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4445,6 +4946,23 @@
         <v>14</v>
       </c>
       <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>15401.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4576,6 +5094,23 @@
         <v>14</v>
       </c>
       <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>1079.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4695,18 +5230,35 @@
       </c>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="n">
-        <v>5663.78</v>
+        <v>5664.27</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="AR32" t="n">
         <v>14</v>
       </c>
       <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>5688.29</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4826,18 +5378,35 @@
       </c>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="n">
-        <v>735.73</v>
+        <v>735.9</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
       </c>
       <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4957,18 +5526,35 @@
       </c>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="n">
-        <v>4928.05</v>
+        <v>4928.37</v>
       </c>
       <c r="AP34" t="n">
         <v>5.27</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="AR34" t="n">
         <v>14</v>
       </c>
       <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>4940.79</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5088,18 +5674,35 @@
       </c>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="n">
-        <v>4720.58</v>
+        <v>4722.53</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.52</v>
+        <v>5.7</v>
       </c>
       <c r="AR35" t="n">
         <v>14</v>
       </c>
       <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>4768.51</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5219,18 +5822,35 @@
       </c>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="n">
-        <v>733.51</v>
+        <v>733.67</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.140000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="AR36" t="n">
         <v>14</v>
       </c>
       <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>742.22</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5350,18 +5970,35 @@
       </c>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="n">
-        <v>2098.92</v>
+        <v>2100.07</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AR37" t="n">
         <v>14</v>
       </c>
       <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>2116.06</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5481,18 +6118,35 @@
       </c>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="n">
-        <v>1036.35</v>
+        <v>1036.9</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="AR38" t="n">
         <v>14</v>
       </c>
       <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>1039.2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5612,18 +6266,35 @@
       </c>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="n">
-        <v>338.23</v>
+        <v>338.21</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="AR39" t="n">
         <v>14</v>
       </c>
       <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5749,12 +6420,29 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-4.58</v>
+        <v>-4.59</v>
       </c>
       <c r="AR40" t="n">
         <v>14</v>
       </c>
       <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>103.43</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5874,18 +6562,35 @@
       </c>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="n">
-        <v>513.59</v>
+        <v>513.6900000000001</v>
       </c>
       <c r="AP41" t="n">
-        <v>15.34</v>
+        <v>15.37</v>
       </c>
       <c r="AQ41" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
       <c r="AR41" t="n">
         <v>14</v>
       </c>
       <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>518.6900000000001</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6005,18 +6710,35 @@
       </c>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="n">
-        <v>1254.27</v>
+        <v>1254.15</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AR42" t="n">
         <v>14</v>
       </c>
       <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>1242.74</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6136,18 +6858,35 @@
       </c>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="n">
-        <v>905.47</v>
+        <v>905.55</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="AR43" t="n">
         <v>14</v>
       </c>
       <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>902.89</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6267,18 +7006,35 @@
       </c>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="n">
-        <v>491.52</v>
+        <v>490.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-6.68</v>
+        <v>-7.45</v>
       </c>
       <c r="AR44" t="n">
         <v>14</v>
       </c>
       <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>482.11</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6398,18 +7154,35 @@
       </c>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="n">
-        <v>6893.08</v>
+        <v>6893.27</v>
       </c>
       <c r="AP45" t="n">
         <v>4.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="AR45" t="n">
         <v>14</v>
       </c>
       <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>6934.69</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6529,18 +7302,35 @@
       </c>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="n">
-        <v>291.77</v>
+        <v>291.84</v>
       </c>
       <c r="AP46" t="n">
-        <v>-1.38</v>
+        <v>-1.36</v>
       </c>
       <c r="AQ46" t="n">
-        <v>-7.82</v>
+        <v>-7.73</v>
       </c>
       <c r="AR46" t="n">
         <v>14</v>
       </c>
       <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>295.32</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -790,29 +790,29 @@
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>17939.06</v>
+        <v>17938.38</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>18129.3</v>
+        <v>18145.52</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.85</v>
+        <v>5.94</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.31</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -938,29 +938,29 @@
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1633.07</v>
+        <v>1633.32</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.76</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1662.12</v>
+        <v>1669.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.31</v>
+        <v>9.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>16306</v>
+        <v>16305.07</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.12</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
         <v>14</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>16467.18</v>
+        <v>16476.27</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.86</v>
+        <v>5.92</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.01</v>
+        <v>4.27</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1234,29 +1234,29 @@
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>12594.27</v>
+        <v>12594.54</v>
       </c>
       <c r="AP5" t="n">
         <v>6.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>12751.96</v>
+        <v>12763.08</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.43</v>
+        <v>6.52</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.1</v>
+        <v>5.46</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1382,29 +1382,29 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>2307.6</v>
+        <v>2307.32</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.45</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
         <v>14</v>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>2359.03</v>
+        <v>2358.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.220000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1530,29 +1530,29 @@
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>3005.76</v>
+        <v>3004.46</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.81</v>
+        <v>3.63</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>3031.84</v>
+        <v>3032.63</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>2696.66</v>
+        <v>2696.68</v>
       </c>
       <c r="AP8" t="n">
         <v>1.64</v>
@@ -1691,16 +1691,16 @@
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>2695.85</v>
+        <v>2695.73</v>
       </c>
       <c r="AU8" t="n">
         <v>1.08</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1826,29 +1826,29 @@
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>1919.37</v>
+        <v>1919.39</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1935.67</v>
+        <v>1937.05</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.44</v>
+        <v>3.73</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>1090.15</v>
+        <v>1090.16</v>
       </c>
       <c r="AP10" t="n">
         <v>4.08</v>
@@ -1987,16 +1987,16 @@
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1104.06</v>
+        <v>1105.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>5.56</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2122,29 +2122,29 @@
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>2664.87</v>
+        <v>2666.68</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.17</v>
+        <v>17.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.13</v>
+        <v>11.43</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>2729.57</v>
+        <v>2739.66</v>
       </c>
       <c r="AU11" t="n">
-        <v>14.82</v>
+        <v>15.24</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.07</v>
+        <v>11.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
@@ -2270,29 +2270,29 @@
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>5505.5</v>
+        <v>5506.53</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.81</v>
+        <v>3.89</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>5442.53</v>
+        <v>5448.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AV12" t="n">
-        <v>-4.5</v>
+        <v>-4.16</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2418,29 +2418,29 @@
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>4590.04</v>
+        <v>4591.02</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>4526.75</v>
+        <v>4535.49</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AV13" t="n">
-        <v>-5.4</v>
+        <v>-4.75</v>
       </c>
       <c r="AW13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2566,29 +2566,29 @@
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>1840.28</v>
+        <v>1840.44</v>
       </c>
       <c r="AP14" t="n">
-        <v>-3.94</v>
+        <v>-3.93</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-12.14</v>
+        <v>-12.11</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>1879.34</v>
+        <v>1879.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -2714,29 +2714,29 @@
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>22148.59</v>
+        <v>22148.79</v>
       </c>
       <c r="AP15" t="n">
         <v>5.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>22336.09</v>
+        <v>22356.09</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
@@ -2862,29 +2862,29 @@
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>1352.71</v>
+        <v>1353.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-4.84</v>
+        <v>-4.52</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
-        <v>1374.82</v>
+        <v>1385.97</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.5</v>
+        <v>10.39</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.7</v>
+        <v>9.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -3023,16 +3023,16 @@
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>12441.01</v>
+        <v>12453.63</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.78</v>
+        <v>6.89</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.53</v>
+        <v>5.96</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3171,16 +3171,16 @@
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
-        <v>914.62</v>
+        <v>922.95</v>
       </c>
       <c r="AU18" t="n">
-        <v>10.7</v>
+        <v>11.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.01</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
@@ -3319,16 +3319,16 @@
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
-        <v>11526.39</v>
+        <v>11530.68</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.33</v>
+        <v>5.49</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>7983.45</v>
+        <v>7991.58</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.25</v>
+        <v>7.36</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>6.23</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
@@ -3615,16 +3615,16 @@
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1616.81</v>
+        <v>1615.89</v>
       </c>
       <c r="AU21" t="n">
-        <v>11.22</v>
+        <v>11.16</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.35</v>
+        <v>11.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
@@ -3763,16 +3763,16 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>915.78</v>
+        <v>917.08</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.53</v>
+        <v>5.12</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>1656.65</v>
+        <v>1656.95</v>
       </c>
       <c r="AU23" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.75</v>
+        <v>-0.68</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>1583.32</v>
+        <v>1583.94</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="AW24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
@@ -4207,16 +4207,16 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1000.63</v>
+        <v>1001.35</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AW25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
@@ -4355,16 +4355,16 @@
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
-        <v>2210.88</v>
+        <v>2217.72</v>
       </c>
       <c r="AU26" t="n">
-        <v>15.64</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.57</v>
+        <v>12.96</v>
       </c>
       <c r="AW26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
@@ -4503,16 +4503,16 @@
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>4199.79</v>
+        <v>4203.88</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AV27" t="n">
-        <v>-4.76</v>
+        <v>-4.39</v>
       </c>
       <c r="AW27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
@@ -4651,16 +4651,16 @@
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
-        <v>3623.86</v>
+        <v>3630.59</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="AV28" t="n">
-        <v>-6.42</v>
+        <v>-5.72</v>
       </c>
       <c r="AW28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -4799,16 +4799,16 @@
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>1397.23</v>
+        <v>1391.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.55</v>
+        <v>3.09</v>
       </c>
       <c r="AV29" t="n">
-        <v>14.82</v>
+        <v>12.79</v>
       </c>
       <c r="AW29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
@@ -4947,16 +4947,16 @@
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
-        <v>15401.4</v>
+        <v>15410.96</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.76</v>
+        <v>5.82</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -5095,16 +5095,16 @@
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>1079.5</v>
+        <v>1086.99</v>
       </c>
       <c r="AU31" t="n">
-        <v>10.43</v>
+        <v>11.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.21</v>
+        <v>10.22</v>
       </c>
       <c r="AW31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -5230,29 +5230,29 @@
       </c>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="n">
-        <v>5664.27</v>
+        <v>5663.59</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="AR32" t="n">
         <v>14</v>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>5688.29</v>
+        <v>5691.89</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -5378,29 +5378,29 @@
       </c>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="n">
-        <v>735.9</v>
+        <v>736.15</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>747.5</v>
+        <v>746.3</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.46</v>
+        <v>5.63</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
@@ -5526,29 +5526,29 @@
       </c>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="n">
-        <v>4928.37</v>
+        <v>4927.44</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
       <c r="AR34" t="n">
         <v>14</v>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>4940.79</v>
+        <v>4945.59</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -5674,29 +5674,29 @@
       </c>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="n">
-        <v>4722.53</v>
+        <v>4722.8</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="AR35" t="n">
         <v>14</v>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>4768.51</v>
+        <v>4771.49</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.07</v>
+        <v>5.14</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.95</v>
+        <v>4.19</v>
       </c>
       <c r="AW35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -5822,29 +5822,29 @@
       </c>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="n">
-        <v>733.67</v>
+        <v>733.39</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.24</v>
+        <v>8.07</v>
       </c>
       <c r="AR36" t="n">
         <v>14</v>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>742.22</v>
+        <v>742.12</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.78</v>
+        <v>5.76</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="AW36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -5970,29 +5970,29 @@
       </c>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="n">
-        <v>2100.07</v>
+        <v>2098.77</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="AR37" t="n">
         <v>14</v>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>2116.06</v>
+        <v>2115.55</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AW37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="n">
-        <v>1036.9</v>
+        <v>1036.92</v>
       </c>
       <c r="AP38" t="n">
         <v>3.72</v>
@@ -6131,16 +6131,16 @@
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1039.2</v>
+        <v>1038.78</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
       <c r="AW38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
@@ -6266,29 +6266,29 @@
       </c>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="n">
-        <v>338.21</v>
+        <v>338.23</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14.5</v>
+        <v>14.54</v>
       </c>
       <c r="AR39" t="n">
         <v>14</v>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>352.34</v>
+        <v>353.11</v>
       </c>
       <c r="AU39" t="n">
-        <v>11.19</v>
+        <v>11.43</v>
       </c>
       <c r="AV39" t="n">
-        <v>17.8</v>
+        <v>18.78</v>
       </c>
       <c r="AW39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
@@ -6414,29 +6414,29 @@
       </c>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="n">
-        <v>95.25</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="AP40" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-4.59</v>
+        <v>-4.56</v>
       </c>
       <c r="AR40" t="n">
         <v>14</v>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>103.43</v>
+        <v>103.66</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.35</v>
+        <v>6.59</v>
       </c>
       <c r="AV40" t="n">
-        <v>39.02</v>
+        <v>40.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
@@ -6562,29 +6562,29 @@
       </c>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="n">
-        <v>513.6900000000001</v>
+        <v>515.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>15.37</v>
+        <v>15.77</v>
       </c>
       <c r="AQ41" t="n">
-        <v>8.92</v>
+        <v>10.46</v>
       </c>
       <c r="AR41" t="n">
         <v>14</v>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>518.6900000000001</v>
+        <v>521.9400000000001</v>
       </c>
       <c r="AU41" t="n">
-        <v>11.45</v>
+        <v>12.15</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.95</v>
+        <v>5.09</v>
       </c>
       <c r="AW41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -6710,29 +6710,29 @@
       </c>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="n">
-        <v>1254.15</v>
+        <v>1255.18</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AR42" t="n">
         <v>14</v>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1242.74</v>
+        <v>1244.42</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>-3.59</v>
+        <v>-3.38</v>
       </c>
       <c r="AW42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -6858,29 +6858,29 @@
       </c>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="n">
-        <v>905.55</v>
+        <v>906.53</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.77</v>
+        <v>4.89</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6.01</v>
+        <v>6.47</v>
       </c>
       <c r="AR43" t="n">
         <v>14</v>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>902.89</v>
+        <v>904.89</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AV43" t="n">
-        <v>-1.17</v>
+        <v>-0.72</v>
       </c>
       <c r="AW43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="n">
-        <v>490.5</v>
+        <v>490.66</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-7.45</v>
+        <v>-7.33</v>
       </c>
       <c r="AR44" t="n">
         <v>14</v>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>482.11</v>
+        <v>488.19</v>
       </c>
       <c r="AU44" t="n">
-        <v>-2.38</v>
+        <v>-1.15</v>
       </c>
       <c r="AV44" t="n">
-        <v>-6.67</v>
+        <v>-2</v>
       </c>
       <c r="AW44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -7154,29 +7154,29 @@
       </c>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="n">
-        <v>6893.27</v>
+        <v>6893.48</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="AR45" t="n">
         <v>14</v>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>6934.69</v>
+        <v>6945.13</v>
       </c>
       <c r="AU45" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="AW45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -7302,29 +7302,29 @@
       </c>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="n">
-        <v>291.84</v>
+        <v>292.97</v>
       </c>
       <c r="AP46" t="n">
-        <v>-1.36</v>
+        <v>-0.98</v>
       </c>
       <c r="AQ46" t="n">
-        <v>-7.73</v>
+        <v>-6.3</v>
       </c>
       <c r="AR46" t="n">
         <v>14</v>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
-        <v>295.32</v>
+        <v>298.98</v>
       </c>
       <c r="AU46" t="n">
-        <v>6.21</v>
+        <v>7.53</v>
       </c>
       <c r="AV46" t="n">
-        <v>4.86</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AW46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -7359,23 +7359,23 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>17640.27</v>
+        <v>17615.1</v>
       </c>
       <c r="G47" t="n">
         <v>1.83</v>
       </c>
       <c r="H47" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>17784.17</v>
+        <v>17758.47</v>
       </c>
       <c r="L47" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="M47" t="n">
         <v>3.3</v>
@@ -7385,87 +7385,83 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>17913.07</v>
+        <v>17886.23</v>
       </c>
       <c r="Q47" t="n">
         <v>3.03</v>
       </c>
       <c r="R47" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="n">
-        <v>18058.3</v>
+        <v>18031.4</v>
       </c>
       <c r="V47" t="n">
         <v>3.36</v>
       </c>
       <c r="W47" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="X47" t="n">
         <v>3</v>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>18207.57</v>
+        <v>18181.03</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AC47" t="n">
         <v>3</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>18461.47</v>
+        <v>18435.07</v>
       </c>
       <c r="AF47" t="n">
         <v>3.81</v>
       </c>
       <c r="AG47" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="AH47" t="n">
         <v>3</v>
       </c>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="n">
-        <v>18797.33</v>
+        <v>18769.53</v>
       </c>
       <c r="AK47" t="n">
         <v>4.94</v>
       </c>
       <c r="AL47" t="n">
-        <v>7.48</v>
+        <v>7.46</v>
       </c>
       <c r="AM47" t="n">
         <v>3</v>
       </c>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="n">
-        <v>19058.4</v>
+        <v>19075.13</v>
       </c>
       <c r="AP47" t="n">
-        <v>5.54</v>
+        <v>5.79</v>
       </c>
       <c r="AQ47" t="n">
-        <v>5.67</v>
+        <v>6.67</v>
       </c>
       <c r="AR47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AS47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7494,7 +7490,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5404.43</v>
+        <v>5401.57</v>
       </c>
       <c r="G48" t="n">
         <v>8.33</v>
@@ -7507,100 +7503,96 @@
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>5525.73</v>
+        <v>5523.07</v>
       </c>
       <c r="L48" t="n">
         <v>9.35</v>
       </c>
       <c r="M48" t="n">
-        <v>9.279999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="N48" t="n">
         <v>3</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>5574.7</v>
+        <v>5571.43</v>
       </c>
       <c r="Q48" t="n">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="R48" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="n">
-        <v>5653.3</v>
+        <v>5649.67</v>
       </c>
       <c r="V48" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="W48" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="X48" t="n">
         <v>3</v>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>6191.63</v>
+        <v>6188.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>14.57</v>
+        <v>14.56</v>
       </c>
       <c r="AB48" t="n">
-        <v>43.88</v>
+        <v>43.94</v>
       </c>
       <c r="AC48" t="n">
         <v>3</v>
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>6751.43</v>
+        <v>6748.17</v>
       </c>
       <c r="AF48" t="n">
         <v>22.18</v>
       </c>
       <c r="AG48" t="n">
-        <v>41.37</v>
+        <v>41.4</v>
       </c>
       <c r="AH48" t="n">
         <v>3</v>
       </c>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="n">
-        <v>6935.87</v>
+        <v>6935.47</v>
       </c>
       <c r="AK48" t="n">
-        <v>24.42</v>
+        <v>24.48</v>
       </c>
       <c r="AL48" t="n">
-        <v>11.38</v>
+        <v>11.57</v>
       </c>
       <c r="AM48" t="n">
         <v>3</v>
       </c>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="n">
-        <v>7107.9</v>
+        <v>7146.83</v>
       </c>
       <c r="AP48" t="n">
-        <v>25.73</v>
+        <v>26.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>10.3</v>
+        <v>12.76</v>
       </c>
       <c r="AR48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AS48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7629,46 +7621,46 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>10647.63</v>
+        <v>10631.53</v>
       </c>
       <c r="G49" t="n">
         <v>-1.28</v>
       </c>
       <c r="H49" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>10705.2</v>
+        <v>10688.37</v>
       </c>
       <c r="L49" t="n">
         <v>-0.14</v>
       </c>
       <c r="M49" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="N49" t="n">
         <v>3</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>10807.7</v>
+        <v>10790.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R49" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="n">
-        <v>10878.73</v>
+        <v>10861.5</v>
       </c>
       <c r="V49" t="n">
         <v>3.02</v>
@@ -7681,61 +7673,57 @@
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>10503.43</v>
+        <v>10486.53</v>
       </c>
       <c r="AA49" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="AB49" t="n">
-        <v>-13.1</v>
+        <v>-13.11</v>
       </c>
       <c r="AC49" t="n">
         <v>3</v>
       </c>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>10210.83</v>
+        <v>10193.67</v>
       </c>
       <c r="AF49" t="n">
-        <v>-4.62</v>
+        <v>-4.63</v>
       </c>
       <c r="AG49" t="n">
-        <v>-10.69</v>
+        <v>-10.71</v>
       </c>
       <c r="AH49" t="n">
         <v>3</v>
       </c>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="n">
-        <v>10359.1</v>
+        <v>10338.17</v>
       </c>
       <c r="AK49" t="n">
-        <v>-4.15</v>
+        <v>-4.19</v>
       </c>
       <c r="AL49" t="n">
-        <v>5.94</v>
+        <v>5.79</v>
       </c>
       <c r="AM49" t="n">
         <v>3</v>
       </c>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="n">
-        <v>10444.5</v>
+        <v>10427.27</v>
       </c>
       <c r="AP49" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AR49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AS49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7764,113 +7752,109 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1588.2</v>
+        <v>1582</v>
       </c>
       <c r="G50" t="n">
         <v>2.57</v>
       </c>
       <c r="H50" t="n">
-        <v>-10.11</v>
+        <v>-10.2</v>
       </c>
       <c r="I50" t="n">
         <v>3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
-        <v>1553.23</v>
+        <v>1547.03</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.16</v>
+        <v>-4.19</v>
       </c>
       <c r="M50" t="n">
-        <v>-8.52</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>3</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>1530.67</v>
+        <v>1524.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>-5.5</v>
+        <v>-5.52</v>
       </c>
       <c r="R50" t="n">
-        <v>-5.69</v>
+        <v>-5.72</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="n">
-        <v>1526.27</v>
+        <v>1520.23</v>
       </c>
       <c r="V50" t="n">
-        <v>-6.43</v>
+        <v>-6.45</v>
       </c>
       <c r="W50" t="n">
-        <v>-1.14</v>
+        <v>-1.09</v>
       </c>
       <c r="X50" t="n">
         <v>3</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>1512.5</v>
+        <v>1506.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>-4.77</v>
+        <v>-4.79</v>
       </c>
       <c r="AB50" t="n">
-        <v>-3.56</v>
+        <v>-3.64</v>
       </c>
       <c r="AC50" t="n">
         <v>3</v>
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>1499.2</v>
+        <v>1493.23</v>
       </c>
       <c r="AF50" t="n">
         <v>-3.48</v>
       </c>
       <c r="AG50" t="n">
-        <v>-3.47</v>
+        <v>-3.4</v>
       </c>
       <c r="AH50" t="n">
         <v>3</v>
       </c>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="n">
-        <v>1502.37</v>
+        <v>1495.9</v>
       </c>
       <c r="AK50" t="n">
-        <v>-1.85</v>
+        <v>-1.87</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AM50" t="n">
         <v>3</v>
       </c>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="n">
-        <v>1506</v>
+        <v>1501.03</v>
       </c>
       <c r="AP50" t="n">
-        <v>-1.33</v>
+        <v>-1.26</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.97</v>
+        <v>1.38</v>
       </c>
       <c r="AR50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AS50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7990,22 +7974,18 @@
       </c>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="n">
-        <v>3063.35</v>
+        <v>3070.57</v>
       </c>
       <c r="AP51" t="n">
-        <v>5.37</v>
+        <v>5.62</v>
       </c>
       <c r="AQ51" t="n">
-        <v>5.49</v>
+        <v>6.49</v>
       </c>
       <c r="AR51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>QTD</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AS51" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">

--- a/data/h8-quarterly.xlsx
+++ b/data/h8-quarterly.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>17938.38</v>
+        <v>17938.39</v>
       </c>
       <c r="AP2" t="n">
         <v>5.98</v>
@@ -803,16 +803,16 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>18145.52</v>
+        <v>18134.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="AW2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -938,29 +938,29 @@
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1633.32</v>
+        <v>1633.38</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1669.25</v>
+        <v>1674.79</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.09</v>
+        <v>10.53</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>16305.07</v>
+        <v>16305.01</v>
       </c>
       <c r="AP4" t="n">
         <v>5.98</v>
@@ -1099,16 +1099,16 @@
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>16476.27</v>
+        <v>16459.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.92</v>
+        <v>5.81</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.27</v>
+        <v>3.84</v>
       </c>
       <c r="AW4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1234,29 +1234,29 @@
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>12594.54</v>
+        <v>12594.75</v>
       </c>
       <c r="AP5" t="n">
         <v>6.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>12763.08</v>
+        <v>12759</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.52</v>
+        <v>6.49</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.46</v>
+        <v>5.32</v>
       </c>
       <c r="AW5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>2307.32</v>
+        <v>2307.33</v>
       </c>
       <c r="AP6" t="n">
         <v>7.58</v>
@@ -1395,16 +1395,16 @@
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>2358.01</v>
+        <v>2357.39</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1530,29 +1530,29 @@
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>3004.46</v>
+        <v>3004.52</v>
       </c>
       <c r="AP7" t="n">
         <v>3.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>3032.63</v>
+        <v>3029.91</v>
       </c>
       <c r="AU7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV7" t="n">
         <v>3.42</v>
       </c>
-      <c r="AV7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AW7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1678,29 +1678,29 @@
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>2696.68</v>
+        <v>2696.72</v>
       </c>
       <c r="AP8" t="n">
         <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>2695.73</v>
+        <v>2698.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1826,29 +1826,29 @@
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>1919.39</v>
+        <v>1919.49</v>
       </c>
       <c r="AP9" t="n">
         <v>5.09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.51</v>
+        <v>5.53</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1937.05</v>
+        <v>1930.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.71</v>
+        <v>4.34</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.73</v>
+        <v>2.21</v>
       </c>
       <c r="AW9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -1974,29 +1974,29 @@
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>1090.16</v>
+        <v>1090.26</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR10" t="n">
         <v>14</v>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1105.01</v>
+        <v>1098.07</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.36</v>
+        <v>3.71</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.56</v>
+        <v>2.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2122,29 +2122,29 @@
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>2666.68</v>
+        <v>2666.69</v>
       </c>
       <c r="AP11" t="n">
         <v>17.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>2739.66</v>
+        <v>2743.07</v>
       </c>
       <c r="AU11" t="n">
-        <v>15.24</v>
+        <v>15.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.4</v>
+        <v>11.96</v>
       </c>
       <c r="AW11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>5506.53</v>
+        <v>5506.56</v>
       </c>
       <c r="AP12" t="n">
         <v>3.03</v>
@@ -2283,16 +2283,16 @@
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>5448.3</v>
+        <v>5455.21</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AV12" t="n">
-        <v>-4.16</v>
+        <v>-3.68</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>4591.02</v>
+        <v>4591.03</v>
       </c>
       <c r="AP13" t="n">
         <v>3.26</v>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>4535.49</v>
+        <v>4540.67</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AV13" t="n">
-        <v>-4.75</v>
+        <v>-4.32</v>
       </c>
       <c r="AW13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2566,29 +2566,29 @@
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>1840.44</v>
+        <v>1840.27</v>
       </c>
       <c r="AP14" t="n">
-        <v>-3.93</v>
+        <v>-3.94</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-12.11</v>
+        <v>-12.14</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>1879.2</v>
+        <v>1880.07</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.69</v>
+        <v>8.94</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>22148.79</v>
+        <v>22148.85</v>
       </c>
       <c r="AP15" t="n">
         <v>5.18</v>
@@ -2727,16 +2727,16 @@
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>22356.09</v>
+        <v>22357.23</v>
       </c>
       <c r="AU15" t="n">
         <v>5.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AW15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>1353.84</v>
+        <v>1353.86</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>-4.52</v>
@@ -2875,16 +2875,16 @@
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
-        <v>1385.97</v>
+        <v>1402.27</v>
       </c>
       <c r="AU16" t="n">
-        <v>10.39</v>
+        <v>11.68</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.84</v>
+        <v>15.09</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -3023,16 +3023,16 @@
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>12453.63</v>
+        <v>12448.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.96</v>
+        <v>5.79</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3158,29 +3158,29 @@
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>897.17</v>
+        <v>897.21</v>
       </c>
       <c r="AP18" t="n">
         <v>11.23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-1.36</v>
+        <v>-1.35</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
-        <v>922.95</v>
+        <v>930.9400000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>11.71</v>
+        <v>12.67</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>15.91</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
-        <v>11377.62</v>
+        <v>11377.58</v>
       </c>
       <c r="AP19" t="n">
         <v>6.3</v>
@@ -3319,16 +3319,16 @@
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
-        <v>11530.68</v>
+        <v>11517.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.52</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.49</v>
+        <v>5.02</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>7991.58</v>
+        <v>7996.06</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.23</v>
+        <v>6.47</v>
       </c>
       <c r="AW20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
@@ -3615,16 +3615,16 @@
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1615.89</v>
+        <v>1615.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>11.16</v>
+        <v>11.15</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="AW21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
@@ -3763,16 +3763,16 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>917.08</v>
+        <v>915.23</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.12</v>
+        <v>4.28</v>
       </c>
       <c r="AW22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>1656.95</v>
+        <v>1659.91</v>
       </c>
       <c r="AU23" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.68</v>
+        <v>0.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4059,16 +4059,16 @@
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>1583.94</v>
+        <v>1584.26</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
@@ -4207,16 +4207,16 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1001.35</v>
+        <v>1002.05</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.14</v>
+        <v>4.21</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="AW25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
@@ -4355,16 +4355,16 @@
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
-        <v>2217.72</v>
+        <v>2220.97</v>
       </c>
       <c r="AU26" t="n">
-        <v>16</v>
+        <v>16.17</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.96</v>
+        <v>13.62</v>
       </c>
       <c r="AW26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
@@ -4503,16 +4503,16 @@
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>4203.88</v>
+        <v>4211.84</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AV27" t="n">
-        <v>-4.39</v>
+        <v>-3.67</v>
       </c>
       <c r="AW27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
@@ -4651,16 +4651,16 @@
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
-        <v>3630.59</v>
+        <v>3637.09</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="AV28" t="n">
-        <v>-5.72</v>
+        <v>-5.05</v>
       </c>
       <c r="AW28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -4799,16 +4799,16 @@
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>1391.01</v>
+        <v>1392.63</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="AV29" t="n">
-        <v>12.79</v>
+        <v>13.32</v>
       </c>
       <c r="AW29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
@@ -4947,16 +4947,16 @@
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
-        <v>15410.96</v>
+        <v>15421.89</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.14</v>
+        <v>4.44</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -5095,16 +5095,16 @@
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>1086.99</v>
+        <v>1106.76</v>
       </c>
       <c r="AU31" t="n">
-        <v>11.2</v>
+        <v>13.22</v>
       </c>
       <c r="AV31" t="n">
-        <v>10.22</v>
+        <v>18.46</v>
       </c>
       <c r="AW31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -5243,16 +5243,16 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>5691.89</v>
+        <v>5685.45</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.92</v>
+        <v>3.81</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AW32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -5378,29 +5378,29 @@
       </c>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="n">
-        <v>736.15</v>
+        <v>736.17</v>
       </c>
       <c r="AP33" t="n">
         <v>0.23</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>746.3</v>
+        <v>743.85</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.11</v>
+        <v>-0.22</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.63</v>
+        <v>4.23</v>
       </c>
       <c r="AW33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="n">
-        <v>4927.44</v>
+        <v>4927.42</v>
       </c>
       <c r="AP34" t="n">
         <v>5.25</v>
@@ -5539,16 +5539,16 @@
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>4945.59</v>
+        <v>4941.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AW34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -5674,29 +5674,29 @@
       </c>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="n">
-        <v>4722.8</v>
+        <v>4723.01</v>
       </c>
       <c r="AP35" t="n">
         <v>5.39</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="AR35" t="n">
         <v>14</v>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>4771.49</v>
+        <v>4762.94</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.14</v>
+        <v>4.95</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.19</v>
+        <v>3.42</v>
       </c>
       <c r="AW35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -5828,23 +5828,23 @@
         <v>5.06</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.07</v>
+        <v>8.08</v>
       </c>
       <c r="AR36" t="n">
         <v>14</v>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>742.12</v>
+        <v>741.6900000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.76</v>
+        <v>5.7</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -5970,29 +5970,29 @@
       </c>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="n">
-        <v>2098.77</v>
+        <v>2098.82</v>
       </c>
       <c r="AP37" t="n">
         <v>3.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="AR37" t="n">
         <v>14</v>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>2115.55</v>
+        <v>2114.69</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="AW37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -6118,29 +6118,29 @@
       </c>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="n">
-        <v>1036.92</v>
+        <v>1036.95</v>
       </c>
       <c r="AP38" t="n">
         <v>3.72</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="AR38" t="n">
         <v>14</v>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1038.78</v>
+        <v>1038.69</v>
       </c>
       <c r="AU38" t="n">
         <v>2.87</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AW38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
@@ -6266,29 +6266,29 @@
       </c>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="n">
-        <v>338.23</v>
+        <v>338.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14.54</v>
+        <v>14.67</v>
       </c>
       <c r="AR39" t="n">
         <v>14</v>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>353.11</v>
+        <v>345.77</v>
       </c>
       <c r="AU39" t="n">
-        <v>11.43</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AV39" t="n">
-        <v>18.78</v>
+        <v>9.09</v>
       </c>
       <c r="AW39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
@@ -6414,29 +6414,29 @@
       </c>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="n">
-        <v>95.26000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="AP40" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-4.56</v>
+        <v>-4.14</v>
       </c>
       <c r="AR40" t="n">
         <v>14</v>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>103.66</v>
+        <v>96.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.59</v>
+        <v>-1.27</v>
       </c>
       <c r="AV40" t="n">
-        <v>40.2</v>
+        <v>2.76</v>
       </c>
       <c r="AW40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
@@ -6562,29 +6562,29 @@
       </c>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="n">
-        <v>515.5</v>
+        <v>515.51</v>
       </c>
       <c r="AP41" t="n">
-        <v>15.77</v>
+        <v>15.78</v>
       </c>
       <c r="AQ41" t="n">
-        <v>10.46</v>
+        <v>10.47</v>
       </c>
       <c r="AR41" t="n">
         <v>14</v>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>521.9400000000001</v>
+        <v>522.1</v>
       </c>
       <c r="AU41" t="n">
-        <v>12.15</v>
+        <v>12.19</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.09</v>
+        <v>5.22</v>
       </c>
       <c r="AW41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -6710,29 +6710,29 @@
       </c>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="n">
-        <v>1255.18</v>
+        <v>1255.21</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>14</v>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1244.42</v>
+        <v>1243.37</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="AV42" t="n">
-        <v>-3.38</v>
+        <v>-3.72</v>
       </c>
       <c r="AW42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -6858,29 +6858,29 @@
       </c>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="n">
-        <v>906.53</v>
+        <v>906.54</v>
       </c>
       <c r="AP43" t="n">
         <v>4.89</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6.47</v>
+        <v>6.48</v>
       </c>
       <c r="AR43" t="n">
         <v>14</v>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>904.89</v>
+        <v>903.58</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.72</v>
+        <v>-1.3</v>
       </c>
       <c r="AW43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -7006,29 +7006,29 @@
       </c>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="n">
-        <v>490.66</v>
+        <v>490.49</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-7.33</v>
+        <v>-7.46</v>
       </c>
       <c r="AR44" t="n">
         <v>14</v>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>488.19</v>
+        <v>487.44</v>
       </c>
       <c r="AU44" t="n">
-        <v>-1.15</v>
+        <v>-1.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>-2</v>
+        <v>-2.46</v>
       </c>
       <c r="AW44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="n">
-        <v>6893.48</v>
+        <v>6893.54</v>
       </c>
       <c r="AP45" t="n">
         <v>4.61</v>
@@ -7167,16 +7167,16 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>6945.13</v>
+        <v>6935.34</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.15</v>
+        <v>4.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="AW45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -7302,29 +7302,29 @@
       </c>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="n">
-        <v>292.97</v>
+        <v>292.99</v>
       </c>
       <c r="AP46" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="AQ46" t="n">
-        <v>-6.3</v>
+        <v>-6.28</v>
       </c>
       <c r="AR46" t="n">
         <v>14</v>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
-        <v>298.98</v>
+        <v>295.51</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.53</v>
+        <v>6.28</v>
       </c>
       <c r="AV46" t="n">
-        <v>8.470000000000001</v>
+        <v>3.49</v>
       </c>
       <c r="AW46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
